--- a/data/trans_bre/P16A12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,62</t>
+          <t>-0,56; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,64</t>
+          <t>-0,72; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,02</t>
+          <t>-1,72; 1,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,98</t>
+          <t>-0,53; 0,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,25</t>
+          <t>-1,84; 0,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,39; 117,65</t>
+          <t>-73,61; 176,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,28</t>
+          <t>-2,21; 0,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,31</t>
+          <t>0,11; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,07</t>
+          <t>-1,36; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,21</t>
+          <t>-2,51; 0,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 33,07</t>
+          <t>-83,13; 45,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 1232,55</t>
+          <t>-15,54; 1139,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 168,11</t>
+          <t>-69,71; 185,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,29; 38,67</t>
+          <t>-82,18; 32,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,24</t>
+          <t>-3,72; 1,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,09</t>
+          <t>-2,4; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,09</t>
+          <t>-4,77; -0,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,36</t>
+          <t>-4,32; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 42,56</t>
+          <t>-62,72; 44,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,92; 93,74</t>
+          <t>-49,87; 76,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 1,36</t>
+          <t>-66,72; -3,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 48,42</t>
+          <t>-64,75; 41,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 2,13</t>
+          <t>-6,6; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,61</t>
+          <t>-4,51; 4,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,45</t>
+          <t>-4,81; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -3,33</t>
+          <t>-9,16; -3,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 20,36</t>
+          <t>-46,61; 24,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 49,83</t>
+          <t>-32,06; 47,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 34,06</t>
+          <t>-34,12; 35,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -30,21</t>
+          <t>-60,96; -28,65</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 7,19</t>
+          <t>-4,49; 7,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 2,37</t>
+          <t>-12,11; 1,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 1,86</t>
+          <t>-11,09; 1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -3,78</t>
+          <t>-19,89; -3,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 43,03</t>
+          <t>-19,88; 51,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 9,38</t>
+          <t>-37,16; 7,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 8,56</t>
+          <t>-36,2; 8,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,79; -18,41</t>
+          <t>-79,3; -18,61</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 7,61</t>
+          <t>-6,54; 7,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 9,43</t>
+          <t>-6,62; 8,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 0,47</t>
+          <t>-14,47; -0,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,53</t>
+          <t>-4,02; 6,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 48,23</t>
+          <t>-27,29; 43,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 38,07</t>
+          <t>-19,37; 35,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 1,71</t>
+          <t>-38,58; -0,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 26,29</t>
+          <t>-12,49; 26,33</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,62</t>
+          <t>-0,7; 1,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,41</t>
+          <t>-0,14; 2,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,79</t>
+          <t>-1,85; 0,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,55</t>
+          <t>-2,71; 0,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 31,06</t>
+          <t>-11,46; 32,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 36,34</t>
+          <t>-1,72; 38,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 10,53</t>
+          <t>-20,08; 11,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 5,28</t>
+          <t>-30,4; 9,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A12-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-1,13; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,44</t>
+          <t>-0,57; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-65,66%</t>
+          <t>-60,89%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,65</t>
+          <t>-0,59; 0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,18</t>
+          <t>-1,79; 1,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,95</t>
+          <t>-0,53; 0,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,19</t>
+          <t>-1,81; 0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 176,45</t>
+          <t>-79,43; 149,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,11%</t>
+          <t>-42,22%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,27</t>
+          <t>-2,12; 0,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,34</t>
+          <t>0,17; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,99</t>
+          <t>-1,35; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,12</t>
+          <t>-2,25; 0,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 45,52</t>
+          <t>-83,99; 37,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 1139,47</t>
+          <t>-5,27; 1235,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 185,48</t>
+          <t>-70,3; 158,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,18; 32,14</t>
+          <t>-76,19; 45,81</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-39,49%</t>
+          <t>-54,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,2</t>
+          <t>-3,5; 1,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,95</t>
+          <t>-2,24; 1,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; -0,29</t>
+          <t>-4,89; -0,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,38</t>
+          <t>-5,7; -1,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 44,77</t>
+          <t>-62,64; 38,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,87; 76,6</t>
+          <t>-49,09; 72,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,72; -3,51</t>
+          <t>-69,11; 1,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 41,69</t>
+          <t>-70,39; -26,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,18</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-48,21%</t>
+          <t>-47,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,3</t>
+          <t>-6,26; 2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,44</t>
+          <t>-4,18; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,59</t>
+          <t>-5,21; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -3,11</t>
+          <t>-9,07; -3,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 24,89</t>
+          <t>-43,71; 26,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 47,63</t>
+          <t>-32,06; 52,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 35,51</t>
+          <t>-35,09; 32,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,96; -28,65</t>
+          <t>-61,77; -29,63</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,34</t>
+          <t>-4,15</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,38%</t>
+          <t>-20,6%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 7,86</t>
+          <t>-4,47; 7,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 1,68</t>
+          <t>-12,21; 1,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 1,76</t>
+          <t>-11,22; 1,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,89; -3,76</t>
+          <t>-8,39; -0,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 51,52</t>
+          <t>-19,55; 42,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 7,03</t>
+          <t>-37,28; 6,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 8,89</t>
+          <t>-37,06; 5,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,3; -18,61</t>
+          <t>-36,98; -1,34</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 7,05</t>
+          <t>-7,42; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 8,68</t>
+          <t>-5,62; 9,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,47; -0,25</t>
+          <t>-14,06; 0,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,5</t>
+          <t>-3,86; 6,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 43,32</t>
+          <t>-30,44; 44,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 35,94</t>
+          <t>-16,97; 39,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,58; -0,67</t>
+          <t>-38,51; 2,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 26,33</t>
+          <t>-12,22; 25,38</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-14,96%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,67</t>
+          <t>-0,69; 1,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,54</t>
+          <t>-0,22; 2,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,9</t>
+          <t>-1,75; 1,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,68</t>
+          <t>-2,34; -0,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 32,72</t>
+          <t>-11,07; 29,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 38,14</t>
+          <t>-2,67; 36,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 11,79</t>
+          <t>-19,65; 14,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,49</t>
+          <t>-24,5; -2,26</t>
         </is>
       </c>
     </row>
